--- a/data/trans_dic/P21D_2_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_2_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,71</t>
+          <t>1,23; 4,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,2</t>
+          <t>1,51; 4,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,09</t>
+          <t>1,72; 4,11</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,01</t>
+          <t>0,1; 2,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,51</t>
+          <t>0,75; 2,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,89</t>
+          <t>0,45; 1,85</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,37</t>
+          <t>1,68; 5,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,68</t>
+          <t>0,68; 4,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,65</t>
+          <t>1,35; 3,67</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,97</t>
+          <t>0,23; 1,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,69</t>
+          <t>1,57; 7,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,54</t>
+          <t>1,2; 4,77</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,26</t>
+          <t>0,87; 2,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,58</t>
+          <t>1,65; 3,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,53</t>
+          <t>1,37; 2,59</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria dental, no la pudo recibir por motivos económicos (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3315; 12545</t>
+          <t>3291; 12436</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4502; 15545</t>
+          <t>4520; 14286</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9362; 23133</t>
+          <t>9744; 23256</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>840; 13260</t>
+          <t>629; 13910</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3314; 11238</t>
+          <t>3340; 11038</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5145; 20896</t>
+          <t>4936; 20410</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5270; 17753</t>
+          <t>5567; 18128</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2235; 12121</t>
+          <t>2230; 13311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9192; 24075</t>
+          <t>8917; 24249</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>836; 8020</t>
+          <t>941; 7780</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8171; 39711</t>
+          <t>8083; 36574</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11439; 41945</t>
+          <t>11096; 44069</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15063; 37634</t>
+          <t>14538; 37524</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25945; 56964</t>
+          <t>26281; 59403</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45105; 82350</t>
+          <t>44458; 84305</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_2_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_2_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,66</t>
+          <t>1,72; 5,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,78</t>
+          <t>1,36; 4,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,11</t>
+          <t>1,89; 4,1</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,11</t>
+          <t>0,35; 2,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,47</t>
+          <t>1,06; 3,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,85</t>
+          <t>0,97; 2,69</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,48</t>
+          <t>2,3; 6,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,04</t>
+          <t>1,28; 4,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,67</t>
+          <t>2,12; 4,81</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,91</t>
+          <t>0,21; 2,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,08</t>
+          <t>1,59; 3,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,77</t>
+          <t>1,1; 2,68</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,26</t>
+          <t>1,54; 3,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,73</t>
+          <t>1,81; 3,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,59</t>
+          <t>1,85; 2,82</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15286</t>
+          <t>17859</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3291; 12436</t>
+          <t>4952; 16101</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4520; 14286</t>
+          <t>4392; 14698</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9744; 23256</t>
+          <t>11540; 25048</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>15399</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>629; 13910</t>
+          <t>1637; 11123</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3340; 11038</t>
+          <t>5320; 19143</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4936; 20410</t>
+          <t>9455; 26219</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>24879</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5567; 18128</t>
+          <t>8666; 26004</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2230; 13311</t>
+          <t>4848; 16287</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8917; 24249</t>
+          <t>16019; 36359</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16688</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>15958</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>941; 7780</t>
+          <t>925; 9558</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8083; 36574</t>
+          <t>7797; 19299</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11096; 44069</t>
+          <t>10177; 24728</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25487</t>
+          <t>33541</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>36433</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61921</t>
+          <t>74096</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14538; 37524</t>
+          <t>24192; 48147</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26281; 59403</t>
+          <t>30641; 54152</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44458; 84305</t>
+          <t>60451; 91886</t>
         </is>
       </c>
     </row>
